--- a/naver-place-crawler/results_health/광산구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/광산구_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>와이핏휘트니스 헬스 PT</t>
+          <t>레벨업피트니스 헬스&amp;PT 첨단점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dhkdqkfka300@naver.com</t>
+          <t>wjddbqls0383@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1446-8110</t>
+          <t>0507-1317-9336</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>광주광역시 광산구 하남대로 39 301호</t>
+          <t>광주광역시 광산구 첨단중앙로124번길 79 2층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dhkdqkfka300</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>225</v>
+        <v>745</v>
       </c>
       <c r="Q2" t="n">
-        <v>219</v>
+        <v>1081</v>
       </c>
       <c r="R2" t="n">
-        <v>444</v>
+        <v>1826</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1608825597</t>
+          <t>1078877238</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1608825597</t>
+          <t>https://m.place.naver.com/place/1078877238</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="Q3" t="n">
         <v>701</v>
       </c>
       <c r="R3" t="n">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/place85_1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -794,10 +794,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4s68z</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -812,10 +816,10 @@
         <v>712</v>
       </c>
       <c r="Q4" t="n">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="R4" t="n">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -834,7 +838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -863,12 +867,12 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>광주 광산구 첨단중앙로106번길 29 5층 제로백피트니스</t>
+          <t>광주광역시 광산구 첨단중앙로106번길 29 5층 제로백피트니스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/zeroback2022/223794553588</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,12 +882,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -910,10 +914,10 @@
         <v>628</v>
       </c>
       <c r="Q5" t="n">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="R5" t="n">
-        <v>1668</v>
+        <v>1670</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -932,7 +936,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -944,29 +948,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24시 헬스 PT 제로백피트니스 운남점</t>
+          <t>NS휘트니스 선운점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dnsska0724@naver.com</t>
+          <t>nsfitness_seonun@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1420-8873</t>
+          <t>0507-1427-7668</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>광주광역시 광산구 하남대로 288 햇살빌딩 4층 제로백피트니스</t>
+          <t>광주광역시 광산구 어등대로 555 2동 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dnsska0724</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -976,20 +980,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wh23ln4</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1001,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1105</v>
+        <v>80</v>
       </c>
       <c r="Q6" t="n">
-        <v>312</v>
+        <v>121</v>
       </c>
       <c r="R6" t="n">
-        <v>1417</v>
+        <v>201</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,56 +1024,56 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1165744879</t>
+          <t>2097553652</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1165744879</t>
+          <t>https://m.place.naver.com/place/2097553652</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>짐플릭스 첨단점</t>
+          <t>300평 PT&amp;GX 드림스페이스휘트니스운남점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>gymflix@naver.com</t>
+          <t>ds-unnam@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1364-2795</t>
+          <t>0507-1486-3130</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>광주광역시 광산구 임방울대로800번길 72 3층</t>
+          <t>광주광역시 광산구 목련로153번길 85 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.gymflix.co.kr/</t>
+          <t>https://www.instagram.com/dreamspace_unnam/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1095,13 +1103,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>274</v>
+        <v>228</v>
       </c>
       <c r="Q7" t="n">
-        <v>850</v>
+        <v>238</v>
       </c>
       <c r="R7" t="n">
-        <v>1124</v>
+        <v>466</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,17 +1118,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1955578541</t>
+          <t>1787637585</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1955578541</t>
+          <t>https://m.place.naver.com/place/1787637585</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1174,10 +1182,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wkfba0h</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1214,7 +1226,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1238,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>짐플릭스 선운점</t>
+          <t>짐플릭스 첨단점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1237,13 +1249,13 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1363-2795</t>
+          <t>0507-1364-2795</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>광주광역시 광산구 동곡로 739 7층</t>
+          <t>광주광역시 광산구 임방울대로800번길 72 3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1268,10 +1280,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wkfba0h</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1283,13 +1299,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>118</v>
+        <v>274</v>
       </c>
       <c r="Q9" t="n">
-        <v>659</v>
+        <v>850</v>
       </c>
       <c r="R9" t="n">
-        <v>777</v>
+        <v>1124</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,115 +1314,213 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1174990314</t>
+          <t>1955578541</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1174990314</t>
+          <t>https://m.place.naver.com/place/1955578541</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>리브 필라테스</t>
+          <t>짐플릭스 선운점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>momiyahn@naver.com</t>
+          <t>gymflix@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1430-8033</t>
+          <t>0507-1363-2795</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
+          <t>광주광역시 광산구 동곡로 739 7층</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://www.gymflix.co.kr/</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wkfba0h</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>118</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>659</v>
+      </c>
+      <c r="R10" t="n">
+        <v>777</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1174990314</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1174990314</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>리브 필라테스</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>momiyahn@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1430-8033</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>광주 광산구 사암로 214 4층</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/momiyahn</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w4r4cu</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
         <v>597</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q11" t="n">
         <v>220</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R11" t="n">
         <v>817</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
         <is>
           <t>1043723602</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1043723602</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
